--- a/output/Tables/2019/HIA_per_sex_Rubin.xlsx
+++ b/output/Tables/2019/HIA_per_sex_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24484.382</v>
+        <v>24571.032</v>
       </c>
       <c r="D2">
-        <v>22817.683</v>
+        <v>22900.731</v>
       </c>
       <c r="E2">
-        <v>26151.082</v>
+        <v>26241.332</v>
       </c>
       <c r="F2">
-        <v>286592.527</v>
+        <v>286835.972</v>
       </c>
       <c r="G2">
-        <v>275289.305</v>
+        <v>275509.552</v>
       </c>
       <c r="H2">
-        <v>297895.748</v>
+        <v>298162.392</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38116806030.764</v>
+        <v>38149184279.147</v>
       </c>
       <c r="M2">
-        <v>36613477616.16</v>
+        <v>36642770421.907</v>
       </c>
       <c r="N2">
-        <v>39620134445.368</v>
+        <v>39655598136.388</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34006.945</v>
+        <v>34354.138</v>
       </c>
       <c r="D3">
-        <v>31545.785</v>
+        <v>31839.604</v>
       </c>
       <c r="E3">
-        <v>36468.105</v>
+        <v>36868.672</v>
       </c>
       <c r="F3">
-        <v>318208.661</v>
+        <v>320123.833</v>
       </c>
       <c r="G3">
-        <v>302412.472</v>
+        <v>304202.315</v>
       </c>
       <c r="H3">
-        <v>334004.851</v>
+        <v>336045.351</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42321751970.957</v>
+        <v>42576469756.409</v>
       </c>
       <c r="M3">
-        <v>40220858819.575</v>
+        <v>40458907833.869</v>
       </c>
       <c r="N3">
-        <v>44422645122.339</v>
+        <v>44694031678.949</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18755.572</v>
+        <v>18999.847</v>
       </c>
       <c r="D4">
-        <v>17670.305</v>
+        <v>17906.514</v>
       </c>
       <c r="E4">
-        <v>19840.838</v>
+        <v>20093.181</v>
       </c>
       <c r="F4">
-        <v>19055.024</v>
+        <v>19233.417</v>
       </c>
       <c r="G4">
-        <v>18062.179</v>
+        <v>18236.209</v>
       </c>
       <c r="H4">
-        <v>20047.87</v>
+        <v>20230.626</v>
       </c>
       <c r="I4">
-        <v>1044722848.842</v>
+        <v>1058329492.078</v>
       </c>
       <c r="J4">
-        <v>984271316.625</v>
+        <v>997428636.457</v>
       </c>
       <c r="K4">
-        <v>1105174381.059</v>
+        <v>1119230347.7</v>
       </c>
       <c r="L4">
-        <v>2534318227.983</v>
+        <v>2558044498.351</v>
       </c>
       <c r="M4">
-        <v>2402269786.887</v>
+        <v>2425415774.065</v>
       </c>
       <c r="N4">
-        <v>2666366669.079</v>
+        <v>2690673222.637</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21386.338</v>
+        <v>21691.716</v>
       </c>
       <c r="D5">
-        <v>19915.95</v>
+        <v>20205.763</v>
       </c>
       <c r="E5">
-        <v>22856.725</v>
+        <v>23177.669</v>
       </c>
       <c r="F5">
-        <v>16874.272</v>
+        <v>17058.773</v>
       </c>
       <c r="G5">
-        <v>15759.75</v>
+        <v>15935.228</v>
       </c>
       <c r="H5">
-        <v>17988.795</v>
+        <v>18182.318</v>
       </c>
       <c r="I5">
-        <v>1191261784.668</v>
+        <v>1208271952.961</v>
       </c>
       <c r="J5">
-        <v>1109358249.943</v>
+        <v>1125501401.828</v>
       </c>
       <c r="K5">
-        <v>1273165319.394</v>
+        <v>1291042504.093</v>
       </c>
       <c r="L5">
-        <v>2244278230.873</v>
+        <v>2268816805.486</v>
       </c>
       <c r="M5">
-        <v>2096046728.689</v>
+        <v>2119385269.98</v>
       </c>
       <c r="N5">
-        <v>2392509733.058</v>
+        <v>2418248340.991</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>20118.555</v>
+        <v>19366.334</v>
       </c>
       <c r="D6">
-        <v>18876.184</v>
+        <v>18255.778</v>
       </c>
       <c r="E6">
-        <v>21360.927</v>
+        <v>20476.89</v>
       </c>
       <c r="F6">
-        <v>36182.954</v>
+        <v>34844.069</v>
       </c>
       <c r="G6">
-        <v>33529.201</v>
+        <v>32467.374</v>
       </c>
       <c r="H6">
-        <v>38836.706</v>
+        <v>37220.765</v>
       </c>
       <c r="I6">
-        <v>297895448.539</v>
+        <v>286757307.096</v>
       </c>
       <c r="J6">
-        <v>279499655.932</v>
+        <v>270313300.63</v>
       </c>
       <c r="K6">
-        <v>316291241.146</v>
+        <v>303201313.562</v>
       </c>
       <c r="L6">
-        <v>4812332820.065</v>
+        <v>4634261232.83</v>
       </c>
       <c r="M6">
-        <v>4459383783.973</v>
+        <v>4318160738.08</v>
       </c>
       <c r="N6">
-        <v>5165281856.157</v>
+        <v>4950361727.579</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>11100.139</v>
+        <v>10863.186</v>
       </c>
       <c r="D7">
-        <v>10208.094</v>
+        <v>10048.348</v>
       </c>
       <c r="E7">
-        <v>11992.183</v>
+        <v>11678.023</v>
       </c>
       <c r="F7">
-        <v>10875.367</v>
+        <v>10634.441</v>
       </c>
       <c r="G7">
-        <v>10027.241</v>
+        <v>9849.91</v>
       </c>
       <c r="H7">
-        <v>11723.494</v>
+        <v>11418.973</v>
       </c>
       <c r="I7">
-        <v>164359754.344</v>
+        <v>160851187.724</v>
       </c>
       <c r="J7">
-        <v>151151252.053</v>
+        <v>148785893.065</v>
       </c>
       <c r="K7">
-        <v>177568256.635</v>
+        <v>172916482.383</v>
       </c>
       <c r="L7">
-        <v>1446423824.823</v>
+        <v>1414380713.647</v>
       </c>
       <c r="M7">
-        <v>1333623001.666</v>
+        <v>1310038037.225</v>
       </c>
       <c r="N7">
-        <v>1559224647.98</v>
+        <v>1518723390.068</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3034.604</v>
+        <v>3035.804</v>
       </c>
       <c r="D8">
-        <v>2840.381</v>
+        <v>2859.5</v>
       </c>
       <c r="E8">
-        <v>3228.826</v>
+        <v>3212.109</v>
       </c>
       <c r="F8">
-        <v>6380.127</v>
+        <v>6384.203</v>
       </c>
       <c r="G8">
-        <v>5951.624</v>
+        <v>5993.047</v>
       </c>
       <c r="H8">
-        <v>6808.63</v>
+        <v>6775.359</v>
       </c>
       <c r="I8">
-        <v>228205227.588</v>
+        <v>228295523.289</v>
       </c>
       <c r="J8">
-        <v>213599508.011</v>
+        <v>215037256.589</v>
       </c>
       <c r="K8">
-        <v>242810947.165</v>
+        <v>241553789.989</v>
       </c>
       <c r="L8">
-        <v>848556868.044</v>
+        <v>849098966.169</v>
       </c>
       <c r="M8">
-        <v>791565944.791</v>
+        <v>797075235.554</v>
       </c>
       <c r="N8">
-        <v>905547791.2970001</v>
+        <v>901122696.784</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3370.452</v>
+        <v>3432.065</v>
       </c>
       <c r="D9">
-        <v>3115.701</v>
+        <v>3193.748</v>
       </c>
       <c r="E9">
-        <v>3625.202</v>
+        <v>3670.381</v>
       </c>
       <c r="F9">
-        <v>6124.909</v>
+        <v>6224.776</v>
       </c>
       <c r="G9">
-        <v>5639.892</v>
+        <v>5765.913</v>
       </c>
       <c r="H9">
-        <v>6609.926</v>
+        <v>6683.639</v>
       </c>
       <c r="I9">
-        <v>253461345.501</v>
+        <v>258094695.471</v>
       </c>
       <c r="J9">
-        <v>234303857.073</v>
+        <v>240173068.968</v>
       </c>
       <c r="K9">
-        <v>272618833.928</v>
+        <v>276016321.975</v>
       </c>
       <c r="L9">
-        <v>814612899.642</v>
+        <v>827895222.018</v>
       </c>
       <c r="M9">
-        <v>750105681.215</v>
+        <v>766866466.151</v>
       </c>
       <c r="N9">
-        <v>879120118.069</v>
+        <v>888923977.886</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8521.058999999999</v>
+        <v>8487.482</v>
       </c>
       <c r="D10">
-        <v>7850.549</v>
+        <v>7822.147</v>
       </c>
       <c r="E10">
-        <v>9191.567999999999</v>
+        <v>9152.816000000001</v>
       </c>
       <c r="F10">
-        <v>16973.466</v>
+        <v>17019.33</v>
       </c>
       <c r="G10">
-        <v>15902.145</v>
+        <v>15945.486</v>
       </c>
       <c r="H10">
-        <v>18044.788</v>
+        <v>18093.174</v>
       </c>
       <c r="I10">
-        <v>143486104.186</v>
+        <v>142920704.445</v>
       </c>
       <c r="J10">
-        <v>132195387.186</v>
+        <v>131717137.339</v>
       </c>
       <c r="K10">
-        <v>154776821.185</v>
+        <v>154124271.551</v>
       </c>
       <c r="L10">
-        <v>2257471031.039</v>
+        <v>2263570862.577</v>
       </c>
       <c r="M10">
-        <v>2114985283.955</v>
+        <v>2120749620.831</v>
       </c>
       <c r="N10">
-        <v>2399956778.123</v>
+        <v>2406392104.323</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5413.138</v>
+        <v>5456.946</v>
       </c>
       <c r="D11">
-        <v>4869.917</v>
+        <v>4907.762</v>
       </c>
       <c r="E11">
-        <v>5956.36</v>
+        <v>6006.13</v>
       </c>
       <c r="F11">
-        <v>6281.876</v>
+        <v>6347.527</v>
       </c>
       <c r="G11">
-        <v>5780.848</v>
+        <v>5842.211</v>
       </c>
       <c r="H11">
-        <v>6782.905</v>
+        <v>6852.843</v>
       </c>
       <c r="I11">
-        <v>91151836.77</v>
+        <v>91889510.241</v>
       </c>
       <c r="J11">
-        <v>82004527.34100001</v>
+        <v>82641801.671</v>
       </c>
       <c r="K11">
-        <v>100299146.198</v>
+        <v>101137218.812</v>
       </c>
       <c r="L11">
-        <v>835489566.4910001</v>
+        <v>844221107.505</v>
       </c>
       <c r="M11">
-        <v>768852794.984</v>
+        <v>777014054.475</v>
       </c>
       <c r="N11">
-        <v>902126337.997</v>
+        <v>911428160.536</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>88817.677</v>
+        <v>101160.035</v>
       </c>
       <c r="D12">
-        <v>84348.64599999999</v>
+        <v>96104.618</v>
       </c>
       <c r="E12">
-        <v>93286.70699999999</v>
+        <v>106215.451</v>
       </c>
       <c r="F12">
-        <v>30403.251</v>
+        <v>34384.228</v>
       </c>
       <c r="G12">
-        <v>28365.659</v>
+        <v>32100.177</v>
       </c>
       <c r="H12">
-        <v>32440.844</v>
+        <v>36668.28</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>4043632437.721</v>
+        <v>4573102365.193</v>
       </c>
       <c r="M12">
-        <v>3772632666.344</v>
+        <v>4269323545.248</v>
       </c>
       <c r="N12">
-        <v>4314632209.098</v>
+        <v>4876881185.138</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>37149.661</v>
+        <v>42839.737</v>
       </c>
       <c r="D13">
-        <v>34996.105</v>
+        <v>40353.772</v>
       </c>
       <c r="E13">
-        <v>39303.218</v>
+        <v>45325.702</v>
       </c>
       <c r="F13">
-        <v>10613.377</v>
+        <v>12095.339</v>
       </c>
       <c r="G13">
-        <v>9796.397000000001</v>
+        <v>11167.545</v>
       </c>
       <c r="H13">
-        <v>11430.358</v>
+        <v>13023.134</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1411579177.281</v>
+        <v>1608680122.431</v>
       </c>
       <c r="M13">
-        <v>1302920766.586</v>
+        <v>1485283423.189</v>
       </c>
       <c r="N13">
-        <v>1520237587.975</v>
+        <v>1732076821.672</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/HIA_per_sex_Rubin.xlsx
+++ b/output/Tables/2019/HIA_per_sex_Rubin.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24571.032</v>
+        <v>20546.583</v>
       </c>
       <c r="D2">
-        <v>22900.731</v>
+        <v>19113.747</v>
       </c>
       <c r="E2">
-        <v>26241.332</v>
+        <v>21979.418</v>
       </c>
       <c r="F2">
-        <v>286835.972</v>
+        <v>254621.577</v>
       </c>
       <c r="G2">
-        <v>275509.552</v>
+        <v>244140.946</v>
       </c>
       <c r="H2">
-        <v>298162.392</v>
+        <v>265102.208</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38149184279.147</v>
+        <v>33864669693.848</v>
       </c>
       <c r="M2">
-        <v>36642770421.907</v>
+        <v>32470745770.707</v>
       </c>
       <c r="N2">
-        <v>39655598136.388</v>
+        <v>35258593616.989</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34354.138</v>
+        <v>30812.36</v>
       </c>
       <c r="D3">
-        <v>31839.604</v>
+        <v>28497.041</v>
       </c>
       <c r="E3">
-        <v>36868.672</v>
+        <v>33127.679</v>
       </c>
       <c r="F3">
-        <v>320123.833</v>
+        <v>297716.221</v>
       </c>
       <c r="G3">
-        <v>304202.315</v>
+        <v>282302.838</v>
       </c>
       <c r="H3">
-        <v>336045.351</v>
+        <v>313129.603</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42576469756.409</v>
+        <v>39596257343.595</v>
       </c>
       <c r="M3">
-        <v>40458907833.869</v>
+        <v>37546277456.665</v>
       </c>
       <c r="N3">
-        <v>44694031678.949</v>
+        <v>41646237230.525</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18999.847</v>
+        <v>15798.975</v>
       </c>
       <c r="D4">
-        <v>17906.514</v>
+        <v>14830.251</v>
       </c>
       <c r="E4">
-        <v>20093.181</v>
+        <v>16767.699</v>
       </c>
       <c r="F4">
-        <v>19233.417</v>
+        <v>23131.008</v>
       </c>
       <c r="G4">
-        <v>18236.209</v>
+        <v>21868.813</v>
       </c>
       <c r="H4">
-        <v>20230.626</v>
+        <v>24393.203</v>
       </c>
       <c r="I4">
-        <v>1058329492.078</v>
+        <v>832526986.74</v>
       </c>
       <c r="J4">
-        <v>997428636.457</v>
+        <v>781480055.1619999</v>
       </c>
       <c r="K4">
-        <v>1119230347.7</v>
+        <v>883573918.317</v>
       </c>
       <c r="L4">
-        <v>2558044498.351</v>
+        <v>3076424069.664</v>
       </c>
       <c r="M4">
-        <v>2425415774.065</v>
+        <v>2908552132.867</v>
       </c>
       <c r="N4">
-        <v>2690673222.637</v>
+        <v>3244296006.462</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21691.716</v>
+        <v>19469.323</v>
       </c>
       <c r="D5">
-        <v>20205.763</v>
+        <v>18047.362</v>
       </c>
       <c r="E5">
-        <v>23177.669</v>
+        <v>20891.284</v>
       </c>
       <c r="F5">
-        <v>17058.773</v>
+        <v>25521.477</v>
       </c>
       <c r="G5">
-        <v>15935.228</v>
+        <v>23754.126</v>
       </c>
       <c r="H5">
-        <v>18182.318</v>
+        <v>27288.828</v>
       </c>
       <c r="I5">
-        <v>1208271952.961</v>
+        <v>1025935988.689</v>
       </c>
       <c r="J5">
-        <v>1125501401.828</v>
+        <v>951005755.124</v>
       </c>
       <c r="K5">
-        <v>1291042504.093</v>
+        <v>1100866222.255</v>
       </c>
       <c r="L5">
-        <v>2268816805.486</v>
+        <v>3394356421.804</v>
       </c>
       <c r="M5">
-        <v>2119385269.98</v>
+        <v>3159298704.334</v>
       </c>
       <c r="N5">
-        <v>2418248340.991</v>
+        <v>3629414139.273</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>19366.334</v>
+        <v>3563.087</v>
       </c>
       <c r="D6">
-        <v>18255.778</v>
+        <v>3333.982</v>
       </c>
       <c r="E6">
-        <v>20476.89</v>
+        <v>3792.191</v>
       </c>
       <c r="F6">
-        <v>34844.069</v>
+        <v>1908.159</v>
       </c>
       <c r="G6">
-        <v>32467.374</v>
+        <v>1787.565</v>
       </c>
       <c r="H6">
-        <v>37220.765</v>
+        <v>2028.753</v>
       </c>
       <c r="I6">
-        <v>286757307.096</v>
+        <v>104466134.355</v>
       </c>
       <c r="J6">
-        <v>270313300.63</v>
+        <v>97749029.30599999</v>
       </c>
       <c r="K6">
-        <v>303201313.562</v>
+        <v>111183239.404</v>
       </c>
       <c r="L6">
-        <v>4634261232.83</v>
+        <v>253785146.379</v>
       </c>
       <c r="M6">
-        <v>4318160738.08</v>
+        <v>237746140.113</v>
       </c>
       <c r="N6">
-        <v>4950361727.579</v>
+        <v>269824152.646</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>10863.186</v>
+        <v>4634.985</v>
       </c>
       <c r="D7">
-        <v>10048.348</v>
+        <v>4209.115</v>
       </c>
       <c r="E7">
-        <v>11678.023</v>
+        <v>5060.855</v>
       </c>
       <c r="F7">
-        <v>10634.441</v>
+        <v>1950.573</v>
       </c>
       <c r="G7">
-        <v>9849.91</v>
+        <v>1775.615</v>
       </c>
       <c r="H7">
-        <v>11418.973</v>
+        <v>2125.531</v>
       </c>
       <c r="I7">
-        <v>160851187.724</v>
+        <v>135893125.12</v>
       </c>
       <c r="J7">
-        <v>148785893.065</v>
+        <v>123407051.041</v>
       </c>
       <c r="K7">
-        <v>172916482.383</v>
+        <v>148379199.199</v>
       </c>
       <c r="L7">
-        <v>1414380713.647</v>
+        <v>259426240.891</v>
       </c>
       <c r="M7">
-        <v>1310038037.225</v>
+        <v>236156836.299</v>
       </c>
       <c r="N7">
-        <v>1518723390.068</v>
+        <v>282695645.483</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3035.804</v>
+        <v>2618.338</v>
       </c>
       <c r="D8">
-        <v>2859.5</v>
+        <v>2457.389</v>
       </c>
       <c r="E8">
-        <v>3212.109</v>
+        <v>2779.286</v>
       </c>
       <c r="F8">
-        <v>6384.203</v>
+        <v>4421.911</v>
       </c>
       <c r="G8">
-        <v>5993.047</v>
+        <v>4146.041</v>
       </c>
       <c r="H8">
-        <v>6775.359</v>
+        <v>4697.781</v>
       </c>
       <c r="I8">
-        <v>228295523.289</v>
+        <v>102641452.37</v>
       </c>
       <c r="J8">
-        <v>215037256.589</v>
+        <v>96332096.758</v>
       </c>
       <c r="K8">
-        <v>241553789.989</v>
+        <v>108950807.983</v>
       </c>
       <c r="L8">
-        <v>849098966.169</v>
+        <v>588114185.397</v>
       </c>
       <c r="M8">
-        <v>797075235.554</v>
+        <v>551423467.052</v>
       </c>
       <c r="N8">
-        <v>901122696.784</v>
+        <v>624804903.743</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3432.065</v>
+        <v>3135.704</v>
       </c>
       <c r="D9">
-        <v>3193.748</v>
+        <v>2904.867</v>
       </c>
       <c r="E9">
-        <v>3670.381</v>
+        <v>3366.542</v>
       </c>
       <c r="F9">
-        <v>6224.776</v>
+        <v>5934.453</v>
       </c>
       <c r="G9">
-        <v>5765.913</v>
+        <v>5458.95</v>
       </c>
       <c r="H9">
-        <v>6683.639</v>
+        <v>6409.957</v>
       </c>
       <c r="I9">
-        <v>258094695.471</v>
+        <v>122922750.79</v>
       </c>
       <c r="J9">
-        <v>240173068.968</v>
+        <v>113873695.753</v>
       </c>
       <c r="K9">
-        <v>276016321.975</v>
+        <v>131971805.827</v>
       </c>
       <c r="L9">
-        <v>827895222.018</v>
+        <v>789282294.517</v>
       </c>
       <c r="M9">
-        <v>766866466.151</v>
+        <v>726040305.7819999</v>
       </c>
       <c r="N9">
-        <v>888923977.886</v>
+        <v>852524283.251</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8487.482</v>
+        <v>6883.4</v>
       </c>
       <c r="D10">
-        <v>7822.147</v>
+        <v>6296.124</v>
       </c>
       <c r="E10">
-        <v>9152.816000000001</v>
+        <v>7470.676</v>
       </c>
       <c r="F10">
-        <v>17019.33</v>
+        <v>7840.219</v>
       </c>
       <c r="G10">
-        <v>15945.486</v>
+        <v>7156.693</v>
       </c>
       <c r="H10">
-        <v>18093.174</v>
+        <v>8523.745000000001</v>
       </c>
       <c r="I10">
-        <v>142920704.445</v>
+        <v>114594840.714</v>
       </c>
       <c r="J10">
-        <v>131717137.339</v>
+        <v>104817867.23</v>
       </c>
       <c r="K10">
-        <v>154124271.551</v>
+        <v>124371814.199</v>
       </c>
       <c r="L10">
-        <v>2263570862.577</v>
+        <v>1042749111.852</v>
       </c>
       <c r="M10">
-        <v>2120749620.831</v>
+        <v>951840146.906</v>
       </c>
       <c r="N10">
-        <v>2406392104.323</v>
+        <v>1133658076.798</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5456.946</v>
+        <v>4795.767</v>
       </c>
       <c r="D11">
-        <v>4907.762</v>
+        <v>4281.556</v>
       </c>
       <c r="E11">
-        <v>6006.13</v>
+        <v>5309.978</v>
       </c>
       <c r="F11">
-        <v>6347.527</v>
+        <v>5472.064</v>
       </c>
       <c r="G11">
-        <v>5842.211</v>
+        <v>4872.161</v>
       </c>
       <c r="H11">
-        <v>6852.843</v>
+        <v>6071.966</v>
       </c>
       <c r="I11">
-        <v>91889510.241</v>
+        <v>79839923.05599999</v>
       </c>
       <c r="J11">
-        <v>82641801.671</v>
+        <v>71279340.06299999</v>
       </c>
       <c r="K11">
-        <v>101137218.812</v>
+        <v>88400506.04899999</v>
       </c>
       <c r="L11">
-        <v>844221107.505</v>
+        <v>727784462.745</v>
       </c>
       <c r="M11">
-        <v>777014054.475</v>
+        <v>647997436.336</v>
       </c>
       <c r="N11">
-        <v>911428160.536</v>
+        <v>807571489.154</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>101160.035</v>
+        <v>87020.442</v>
       </c>
       <c r="D12">
-        <v>96104.618</v>
+        <v>82451.359</v>
       </c>
       <c r="E12">
-        <v>106215.451</v>
+        <v>91589.52499999999</v>
       </c>
       <c r="F12">
-        <v>34384.228</v>
+        <v>34803.917</v>
       </c>
       <c r="G12">
-        <v>32100.177</v>
+        <v>32534.413</v>
       </c>
       <c r="H12">
-        <v>36668.28</v>
+        <v>37073.422</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>4573102365.193</v>
+        <v>4628921010.07</v>
       </c>
       <c r="M12">
-        <v>4269323545.248</v>
+        <v>4327076951.972</v>
       </c>
       <c r="N12">
-        <v>4876881185.138</v>
+        <v>4930765068.168</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>42839.737</v>
+        <v>39196.733</v>
       </c>
       <c r="D13">
-        <v>40353.772</v>
+        <v>36790.789</v>
       </c>
       <c r="E13">
-        <v>45325.702</v>
+        <v>41602.677</v>
       </c>
       <c r="F13">
-        <v>12095.339</v>
+        <v>12953.88</v>
       </c>
       <c r="G13">
-        <v>11167.545</v>
+        <v>11954.733</v>
       </c>
       <c r="H13">
-        <v>13023.134</v>
+        <v>13953.027</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1608680122.431</v>
+        <v>1722866042.728</v>
       </c>
       <c r="M13">
-        <v>1485283423.189</v>
+        <v>1589979552.027</v>
       </c>
       <c r="N13">
-        <v>1732076821.672</v>
+        <v>1855752533.43</v>
       </c>
     </row>
   </sheetData>
